--- a/input/timetable/Политология_.xlsx
+++ b/input/timetable/Политология_.xlsx
@@ -480,7 +480,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1156,6 +1156,19 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -1169,7 +1182,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1328,100 +1341,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1451,6 +1370,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1479,6 +1410,157 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1500,24 +1582,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1536,65 +1600,26 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1604,35 +1629,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1655,6 +1651,84 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1667,15 +1741,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1688,60 +1753,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2151,12 +2162,12 @@
       <c r="A9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
@@ -2179,46 +2190,46 @@
       <c r="B11" s="24">
         <v>2</v>
       </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="92"/>
-      <c r="F11" s="93"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="102"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="66" t="s">
+      <c r="C12" s="103" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="68"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="105"/>
     </row>
     <row r="13" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="68"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="105"/>
     </row>
     <row r="14" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="96"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="107"/>
+      <c r="F14" s="108"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="23" t="s">
@@ -2227,46 +2238,46 @@
       <c r="B15" s="24">
         <v>1</v>
       </c>
-      <c r="C15" s="97"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="99"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="111"/>
     </row>
     <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="72" t="s">
+      <c r="C16" s="115" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="74"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="117"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="82"/>
+      <c r="F17" s="83"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="28">
         <v>4</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="83"/>
+      <c r="D18" s="122"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="123"/>
     </row>
     <row r="19" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="23" t="s">
@@ -2275,46 +2286,46 @@
       <c r="B19" s="24">
         <v>1</v>
       </c>
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="80"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
     </row>
     <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>3</v>
       </c>
-      <c r="C20" s="66"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67" t="s">
+      <c r="C20" s="103"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="68"/>
+      <c r="F20" s="105"/>
     </row>
     <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>4</v>
       </c>
-      <c r="C21" s="84" t="s">
+      <c r="C21" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="86"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="80"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="28">
         <v>5</v>
       </c>
-      <c r="C22" s="87"/>
-      <c r="D22" s="88"/>
-      <c r="E22" s="88"/>
-      <c r="F22" s="89"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="125"/>
+      <c r="E22" s="125"/>
+      <c r="F22" s="126"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="23" t="s">
@@ -2323,44 +2334,44 @@
       <c r="B23" s="24">
         <v>3</v>
       </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="80"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>4</v>
       </c>
-      <c r="C24" s="103" t="s">
+      <c r="C24" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="105"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="71"/>
     </row>
     <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>5</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="112" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="114"/>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="28">
         <v>6</v>
       </c>
-      <c r="C26" s="100"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="102"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="23" t="s">
@@ -2369,48 +2380,48 @@
       <c r="B27" s="24">
         <v>1</v>
       </c>
-      <c r="C27" s="109" t="s">
+      <c r="C27" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="111"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="26">
         <v>2</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="78" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="85"/>
-      <c r="E28" s="85"/>
-      <c r="F28" s="86"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="80"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="26">
         <v>3</v>
       </c>
-      <c r="C29" s="75" t="s">
+      <c r="C29" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
-      <c r="F29" s="77"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="83"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="28">
         <v>5</v>
       </c>
-      <c r="C30" s="112" t="s">
+      <c r="C30" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="113"/>
-      <c r="E30" s="113"/>
-      <c r="F30" s="114"/>
+      <c r="D30" s="85"/>
+      <c r="E30" s="85"/>
+      <c r="F30" s="86"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="32" t="s">
@@ -2419,32 +2430,32 @@
       <c r="B31" s="24">
         <v>1</v>
       </c>
-      <c r="C31" s="115" t="s">
+      <c r="C31" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="117"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="89"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="121"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="123"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="95"/>
     </row>
     <row r="33" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="34"/>
       <c r="B33" s="28">
         <v>3</v>
       </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="125"/>
-      <c r="E33" s="125"/>
-      <c r="F33" s="126"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="98"/>
     </row>
     <row r="34" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="35"/>
@@ -2459,48 +2470,48 @@
       <c r="B35" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="115" t="s">
+      <c r="C35" s="87" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="116"/>
-      <c r="E35" s="116"/>
-      <c r="F35" s="117"/>
+      <c r="D35" s="88"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="89"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="57"/>
       <c r="B36" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="84" t="s">
+      <c r="C36" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="86"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="80"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="57"/>
       <c r="B37" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="118" t="s">
+      <c r="C37" s="90" t="s">
         <v>33</v>
       </c>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
+      <c r="D37" s="91"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="92"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A38" s="41"/>
       <c r="B38" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="106" t="s">
+      <c r="C38" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="107"/>
-      <c r="E38" s="107"/>
-      <c r="F38" s="108"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="74"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
@@ -2520,6 +2531,23 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C38:F38"/>
@@ -2533,23 +2561,6 @@
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -2673,12 +2684,12 @@
       <c r="A9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="42" t="s">
@@ -2701,46 +2712,46 @@
       <c r="B11" s="24">
         <v>1</v>
       </c>
-      <c r="C11" s="137"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
-      <c r="F11" s="139"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="171"/>
+      <c r="E11" s="171"/>
+      <c r="F11" s="172"/>
     </row>
     <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>2</v>
       </c>
-      <c r="C12" s="140" t="s">
+      <c r="C12" s="151" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="142"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
+      <c r="F12" s="153"/>
     </row>
     <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>3</v>
       </c>
-      <c r="C13" s="143" t="s">
+      <c r="C13" s="127" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="145"/>
+      <c r="D13" s="128"/>
+      <c r="E13" s="128"/>
+      <c r="F13" s="129"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="146" t="s">
+      <c r="C14" s="173" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="147"/>
-      <c r="E14" s="147"/>
-      <c r="F14" s="148"/>
+      <c r="D14" s="174"/>
+      <c r="E14" s="174"/>
+      <c r="F14" s="175"/>
     </row>
     <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="23" t="s">
@@ -2749,44 +2760,44 @@
       <c r="B15" s="24">
         <v>1</v>
       </c>
-      <c r="C15" s="149"/>
-      <c r="D15" s="150"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="151"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="177"/>
+      <c r="F15" s="178"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="114"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="140" t="s">
+      <c r="C17" s="151" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="142"/>
+      <c r="D17" s="152"/>
+      <c r="E17" s="152"/>
+      <c r="F17" s="153"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="28">
         <v>4</v>
       </c>
-      <c r="C18" s="155"/>
-      <c r="D18" s="156"/>
-      <c r="E18" s="156"/>
-      <c r="F18" s="157"/>
+      <c r="C18" s="182"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="184"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="23" t="s">
@@ -2795,46 +2806,46 @@
       <c r="B19" s="24">
         <v>1</v>
       </c>
-      <c r="C19" s="164" t="s">
+      <c r="C19" s="130" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165" t="s">
+      <c r="D19" s="131"/>
+      <c r="E19" s="131" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="166"/>
+      <c r="F19" s="132"/>
     </row>
     <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="161" t="s">
+      <c r="C20" s="148" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="163"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="150"/>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>3</v>
       </c>
-      <c r="C21" s="131"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="133"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="166"/>
     </row>
     <row r="22" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="28">
         <v>4</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="135"/>
-      <c r="E22" s="135"/>
-      <c r="F22" s="136"/>
+      <c r="C22" s="167"/>
+      <c r="D22" s="168"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="169"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="23" t="s">
@@ -2843,46 +2854,46 @@
       <c r="B23" s="24">
         <v>1</v>
       </c>
-      <c r="C23" s="152"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="154"/>
+      <c r="C23" s="179"/>
+      <c r="D23" s="180"/>
+      <c r="E23" s="180"/>
+      <c r="F23" s="181"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>2</v>
       </c>
-      <c r="C24" s="158" t="s">
+      <c r="C24" s="133" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="159"/>
-      <c r="E24" s="159"/>
-      <c r="F24" s="160"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="135"/>
     </row>
     <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="140" t="s">
+      <c r="C25" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
-      <c r="F25" s="142"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="152"/>
+      <c r="F25" s="153"/>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="170" t="s">
+      <c r="C26" s="157" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="172"/>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="159"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="23" t="s">
@@ -2891,44 +2902,44 @@
       <c r="B27" s="24">
         <v>1</v>
       </c>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="130"/>
+      <c r="C27" s="161"/>
+      <c r="D27" s="162"/>
+      <c r="E27" s="162"/>
+      <c r="F27" s="163"/>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="26">
         <v>2</v>
       </c>
-      <c r="C28" s="158" t="s">
+      <c r="C28" s="133" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="159"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="160"/>
+      <c r="D28" s="134"/>
+      <c r="E28" s="134"/>
+      <c r="F28" s="135"/>
     </row>
     <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="26">
         <v>3</v>
       </c>
-      <c r="C29" s="143" t="s">
+      <c r="C29" s="127" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="144"/>
-      <c r="E29" s="144"/>
-      <c r="F29" s="145"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="129"/>
     </row>
     <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="28">
         <v>4</v>
       </c>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="177"/>
-      <c r="F30" s="178"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="140"/>
+      <c r="E30" s="140"/>
+      <c r="F30" s="141"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="32" t="s">
@@ -2937,90 +2948,90 @@
       <c r="B31" s="24">
         <v>2</v>
       </c>
-      <c r="C31" s="164" t="s">
+      <c r="C31" s="130" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="165"/>
-      <c r="E31" s="165"/>
-      <c r="F31" s="166"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="132"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C32" s="173" t="s">
+      <c r="C32" s="136" t="s">
         <v>89</v>
       </c>
-      <c r="D32" s="174"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="175"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="138"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="34"/>
       <c r="B33" s="28">
         <v>4</v>
       </c>
-      <c r="C33" s="182"/>
-      <c r="D33" s="183"/>
-      <c r="E33" s="183"/>
-      <c r="F33" s="184"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="146"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="147"/>
     </row>
     <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="59"/>
       <c r="B34" s="60"/>
-      <c r="C34" s="179"/>
-      <c r="D34" s="180"/>
-      <c r="E34" s="180"/>
-      <c r="F34" s="181"/>
+      <c r="C34" s="142"/>
+      <c r="D34" s="143"/>
+      <c r="E34" s="143"/>
+      <c r="F34" s="144"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="51"/>
       <c r="B35" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="167" t="s">
+      <c r="C35" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="168"/>
-      <c r="E35" s="168"/>
-      <c r="F35" s="169"/>
+      <c r="D35" s="155"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="156"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="64"/>
       <c r="B36" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="118" t="s">
+      <c r="C36" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="92"/>
     </row>
     <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="54"/>
       <c r="B37" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="106" t="s">
+      <c r="C37" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="108"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="74"/>
     </row>
     <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="62" t="s">
         <v>49</v>
       </c>
       <c r="B38" s="63"/>
-      <c r="C38" s="127" t="s">
+      <c r="C38" s="160" t="s">
         <v>80</v>
       </c>
-      <c r="D38" s="127"/>
-      <c r="E38" s="127"/>
-      <c r="F38" s="127"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
@@ -3040,20 +3051,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C9:F9"/>
@@ -3070,6 +3067,20 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -3193,12 +3204,12 @@
       <c r="A9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="99" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="42" t="s">
@@ -3221,94 +3232,94 @@
       <c r="B11" s="49">
         <v>2</v>
       </c>
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="154" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="168"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="169"/>
+      <c r="D11" s="155"/>
+      <c r="E11" s="155"/>
+      <c r="F11" s="156"/>
     </row>
     <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="188" t="s">
+      <c r="C12" s="192" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="189"/>
-      <c r="E12" s="189"/>
-      <c r="F12" s="190"/>
+      <c r="D12" s="193"/>
+      <c r="E12" s="193"/>
+      <c r="F12" s="194"/>
     </row>
     <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="194" t="s">
+      <c r="C13" s="207" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="195"/>
-      <c r="E13" s="195"/>
-      <c r="F13" s="196"/>
+      <c r="D13" s="208"/>
+      <c r="E13" s="208"/>
+      <c r="F13" s="209"/>
     </row>
     <row r="14" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="71"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="114"/>
+    </row>
+    <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="23" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="24">
-        <v>3</v>
-      </c>
-      <c r="C15" s="191"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
-      <c r="F15" s="193"/>
-    </row>
-    <row r="16" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+        <v>2</v>
+      </c>
+      <c r="C15" s="185"/>
+      <c r="D15" s="186"/>
+      <c r="E15" s="187" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="188"/>
+    </row>
+    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
-        <v>4</v>
-      </c>
-      <c r="C16" s="161" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="162"/>
-      <c r="E16" s="162"/>
-      <c r="F16" s="163"/>
+        <v>3</v>
+      </c>
+      <c r="C16" s="151"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
+      <c r="F16" s="153"/>
     </row>
     <row r="17" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
-        <v>5</v>
-      </c>
-      <c r="C17" s="197"/>
-      <c r="D17" s="198"/>
-      <c r="E17" s="162" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="163"/>
+        <v>4</v>
+      </c>
+      <c r="C17" s="148" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="150"/>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="29"/>
       <c r="B18" s="28">
-        <v>6</v>
-      </c>
-      <c r="C18" s="134"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="136"/>
+        <v>5</v>
+      </c>
+      <c r="C18" s="167"/>
+      <c r="D18" s="168"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="169"/>
     </row>
     <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="23" t="s">
@@ -3317,48 +3328,48 @@
       <c r="B19" s="24">
         <v>1</v>
       </c>
-      <c r="C19" s="185" t="s">
+      <c r="C19" s="204" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="186"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="187"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="206"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="114"/>
     </row>
     <row r="21" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="61">
         <v>3</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="114"/>
     </row>
     <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="28">
         <v>4</v>
       </c>
-      <c r="C22" s="106" t="s">
+      <c r="C22" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="108"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="74"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="23" t="s">
@@ -3367,44 +3378,44 @@
       <c r="B23" s="24">
         <v>1</v>
       </c>
-      <c r="C23" s="185"/>
-      <c r="D23" s="186"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="187"/>
+      <c r="C23" s="204"/>
+      <c r="D23" s="205"/>
+      <c r="E23" s="205"/>
+      <c r="F23" s="206"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>2</v>
       </c>
-      <c r="C24" s="188" t="s">
+      <c r="C24" s="192" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="189"/>
-      <c r="E24" s="189"/>
-      <c r="F24" s="190"/>
+      <c r="D24" s="193"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="194"/>
     </row>
     <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="112" t="s">
         <v>105</v>
       </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
+      <c r="D25" s="113"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="114"/>
     </row>
     <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="28">
         <v>4</v>
       </c>
-      <c r="C26" s="155"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="157"/>
+      <c r="C26" s="182"/>
+      <c r="D26" s="183"/>
+      <c r="E26" s="183"/>
+      <c r="F26" s="184"/>
     </row>
     <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="23" t="s">
@@ -3413,44 +3424,44 @@
       <c r="B27" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="208" t="s">
+      <c r="C27" s="201" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="209"/>
-      <c r="E27" s="209"/>
-      <c r="F27" s="210"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="202"/>
+      <c r="F27" s="203"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="26">
         <v>4</v>
       </c>
-      <c r="C28" s="188" t="s">
+      <c r="C28" s="192" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="189"/>
-      <c r="E28" s="189"/>
-      <c r="F28" s="190"/>
+      <c r="D28" s="193"/>
+      <c r="E28" s="193"/>
+      <c r="F28" s="194"/>
     </row>
     <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="26">
         <v>5</v>
       </c>
-      <c r="C29" s="202"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="204"/>
+      <c r="C29" s="195"/>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="197"/>
     </row>
     <row r="30" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="28">
         <v>6</v>
       </c>
-      <c r="C30" s="205"/>
-      <c r="D30" s="206"/>
-      <c r="E30" s="206"/>
-      <c r="F30" s="207"/>
+      <c r="C30" s="198"/>
+      <c r="D30" s="199"/>
+      <c r="E30" s="199"/>
+      <c r="F30" s="200"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="50" t="s">
@@ -3459,54 +3470,54 @@
       <c r="B31" s="49">
         <v>1</v>
       </c>
-      <c r="C31" s="164" t="s">
+      <c r="C31" s="130" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="165"/>
-      <c r="E31" s="165"/>
-      <c r="F31" s="166"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="132"/>
     </row>
     <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="112" t="s">
         <v>96</v>
       </c>
-      <c r="D32" s="70"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="71"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="113"/>
+      <c r="F32" s="114"/>
     </row>
     <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="33"/>
       <c r="B33" s="26">
         <v>3</v>
       </c>
-      <c r="C33" s="121"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="123"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="95"/>
     </row>
     <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="52"/>
       <c r="B34" s="53"/>
-      <c r="C34" s="199"/>
-      <c r="D34" s="200"/>
-      <c r="E34" s="200"/>
-      <c r="F34" s="201"/>
+      <c r="C34" s="189"/>
+      <c r="D34" s="190"/>
+      <c r="E34" s="190"/>
+      <c r="F34" s="191"/>
     </row>
     <row r="35" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="62" t="s">
         <v>49</v>
       </c>
       <c r="B35" s="63"/>
-      <c r="C35" s="127" t="s">
+      <c r="C35" s="160" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
+      <c r="D35" s="160"/>
+      <c r="E35" s="160"/>
+      <c r="F35" s="160"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
@@ -3526,9 +3537,20 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C28:F28"/>
@@ -3538,22 +3560,11 @@
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -3711,44 +3722,44 @@
       <c r="B12" s="49">
         <v>2</v>
       </c>
-      <c r="C12" s="208" t="s">
+      <c r="C12" s="201" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="209"/>
-      <c r="E12" s="209"/>
-      <c r="F12" s="210"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="202"/>
+      <c r="F12" s="203"/>
     </row>
     <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>3</v>
       </c>
-      <c r="C13" s="161"/>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162" t="s">
+      <c r="C13" s="148"/>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="163"/>
+      <c r="F13" s="150"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="25"/>
       <c r="B14" s="26">
         <v>4</v>
       </c>
-      <c r="C14" s="241"/>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="243"/>
+      <c r="C14" s="215"/>
+      <c r="D14" s="216"/>
+      <c r="E14" s="216"/>
+      <c r="F14" s="217"/>
     </row>
     <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="27"/>
       <c r="B15" s="28">
         <v>5</v>
       </c>
-      <c r="C15" s="155"/>
-      <c r="D15" s="156"/>
-      <c r="E15" s="156"/>
-      <c r="F15" s="157"/>
+      <c r="C15" s="182"/>
+      <c r="D15" s="183"/>
+      <c r="E15" s="183"/>
+      <c r="F15" s="184"/>
     </row>
     <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="23" t="s">
@@ -3757,32 +3768,32 @@
       <c r="B16" s="24">
         <v>2</v>
       </c>
-      <c r="C16" s="235"/>
-      <c r="D16" s="236"/>
-      <c r="E16" s="236"/>
-      <c r="F16" s="237"/>
+      <c r="C16" s="185"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
+      <c r="F16" s="211"/>
     </row>
     <row r="17" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="238"/>
-      <c r="D17" s="239"/>
-      <c r="E17" s="239"/>
-      <c r="F17" s="240"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="213"/>
+      <c r="E17" s="213"/>
+      <c r="F17" s="214"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A18" s="25"/>
       <c r="B18" s="26">
         <v>4</v>
       </c>
-      <c r="C18" s="217" t="s">
+      <c r="C18" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="218"/>
-      <c r="E18" s="218"/>
-      <c r="F18" s="219"/>
+      <c r="D18" s="219"/>
+      <c r="E18" s="219"/>
+      <c r="F18" s="220"/>
       <c r="S18" s="56"/>
     </row>
     <row r="19" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3790,12 +3801,12 @@
       <c r="B19" s="28">
         <v>5</v>
       </c>
-      <c r="C19" s="106" t="s">
+      <c r="C19" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="108"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="23" t="s">
@@ -3804,36 +3815,36 @@
       <c r="B20" s="24">
         <v>3</v>
       </c>
-      <c r="C20" s="140" t="s">
+      <c r="C20" s="151" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="141"/>
-      <c r="E20" s="141"/>
-      <c r="F20" s="142"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="153"/>
     </row>
     <row r="21" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>4</v>
       </c>
-      <c r="C21" s="140" t="s">
+      <c r="C21" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="142"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="153"/>
     </row>
     <row r="22" spans="1:19" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="29"/>
       <c r="B22" s="28">
         <v>5</v>
       </c>
-      <c r="C22" s="226" t="s">
+      <c r="C22" s="221" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="227"/>
-      <c r="E22" s="227"/>
-      <c r="F22" s="228"/>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="223"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A23" s="23" t="s">
@@ -3842,44 +3853,44 @@
       <c r="B23" s="24">
         <v>2</v>
       </c>
-      <c r="C23" s="229"/>
-      <c r="D23" s="230"/>
-      <c r="E23" s="230"/>
-      <c r="F23" s="231"/>
+      <c r="C23" s="224"/>
+      <c r="D23" s="225"/>
+      <c r="E23" s="225"/>
+      <c r="F23" s="226"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="232"/>
-      <c r="D24" s="233"/>
-      <c r="E24" s="233"/>
-      <c r="F24" s="234"/>
+      <c r="C24" s="227"/>
+      <c r="D24" s="228"/>
+      <c r="E24" s="228"/>
+      <c r="F24" s="229"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>4</v>
       </c>
-      <c r="C25" s="194" t="s">
+      <c r="C25" s="207" t="s">
         <v>100</v>
       </c>
-      <c r="D25" s="195"/>
-      <c r="E25" s="195"/>
-      <c r="F25" s="196"/>
+      <c r="D25" s="208"/>
+      <c r="E25" s="208"/>
+      <c r="F25" s="209"/>
     </row>
     <row r="26" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="29"/>
       <c r="B26" s="28">
         <v>5</v>
       </c>
-      <c r="C26" s="118" t="s">
+      <c r="C26" s="90" t="s">
         <v>100</v>
       </c>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="92"/>
     </row>
     <row r="27" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="23" t="s">
@@ -3888,44 +3899,44 @@
       <c r="B27" s="24">
         <v>2</v>
       </c>
-      <c r="C27" s="214"/>
-      <c r="D27" s="215"/>
-      <c r="E27" s="215"/>
-      <c r="F27" s="216"/>
+      <c r="C27" s="233"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="235"/>
     </row>
     <row r="28" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="30"/>
       <c r="B28" s="61">
         <v>3</v>
       </c>
-      <c r="C28" s="118" t="s">
+      <c r="C28" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="92"/>
     </row>
     <row r="29" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="30"/>
       <c r="B29" s="61">
         <v>4</v>
       </c>
-      <c r="C29" s="217" t="s">
+      <c r="C29" s="218" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="218"/>
-      <c r="E29" s="218"/>
-      <c r="F29" s="219"/>
+      <c r="D29" s="219"/>
+      <c r="E29" s="219"/>
+      <c r="F29" s="220"/>
     </row>
     <row r="30" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="31"/>
       <c r="B30" s="28">
         <v>5</v>
       </c>
-      <c r="C30" s="220"/>
-      <c r="D30" s="221"/>
-      <c r="E30" s="221"/>
-      <c r="F30" s="222"/>
+      <c r="C30" s="236"/>
+      <c r="D30" s="237"/>
+      <c r="E30" s="237"/>
+      <c r="F30" s="238"/>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A31" s="50" t="s">
@@ -3934,32 +3945,32 @@
       <c r="B31" s="49">
         <v>1</v>
       </c>
-      <c r="C31" s="223" t="s">
+      <c r="C31" s="239" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="224"/>
-      <c r="E31" s="224"/>
-      <c r="F31" s="225"/>
+      <c r="D31" s="240"/>
+      <c r="E31" s="240"/>
+      <c r="F31" s="241"/>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A32" s="33"/>
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="211"/>
-      <c r="D32" s="212"/>
-      <c r="E32" s="212"/>
-      <c r="F32" s="213"/>
+      <c r="C32" s="230"/>
+      <c r="D32" s="231"/>
+      <c r="E32" s="231"/>
+      <c r="F32" s="232"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="52"/>
       <c r="B33" s="53">
         <v>3</v>
       </c>
-      <c r="C33" s="182"/>
-      <c r="D33" s="183"/>
-      <c r="E33" s="183"/>
-      <c r="F33" s="184"/>
+      <c r="C33" s="145"/>
+      <c r="D33" s="146"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="147"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
@@ -3979,6 +3990,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C14:F14"/>
@@ -3987,22 +4014,6 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
     <cfRule type="expression" priority="3">

--- a/input/timetable/Политология_.xlsx
+++ b/input/timetable/Политология_.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14190" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14190" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="127">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -122,15 +125,39 @@
     <t>весенний</t>
   </si>
   <si>
+    <t>Вариясова Е.В.</t>
+  </si>
+  <si>
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Мархинин В.В.</t>
+  </si>
+  <si>
+    <t>Ушакова Н.В.</t>
+  </si>
+  <si>
+    <t>Габеркорн А.И.</t>
+  </si>
+  <si>
+    <t>Пуртова В.С.</t>
+  </si>
+  <si>
+    <t>Кнельц И.А.</t>
+  </si>
+  <si>
     <t>История политических учений (лек)/(пр), Г209</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Сердюков Д.В.</t>
+  </si>
+  <si>
+    <t>Забирова В.Х.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
@@ -149,6 +176,12 @@
     <t>101-31</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
+    <t>Сташкин П.Р.</t>
+  </si>
+  <si>
     <t>Сравнительная политология (пр), Г209</t>
   </si>
   <si>
@@ -191,6 +224,9 @@
     <t>История политических учений (лек)/(пр), Г201</t>
   </si>
   <si>
+    <t>Дроздова А.А.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
@@ -230,9 +266,18 @@
     <t>ТО: 02.02.2026-08.06.2026</t>
   </si>
   <si>
+    <t>Пичуева А.В.; Афян К.А.</t>
+  </si>
+  <si>
     <t>Политическая история России и зарубежных стран (пр) Г209</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Ерохина Е.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
@@ -245,6 +290,12 @@
     <t>Муниципальная политика и управление (лек), Г209//</t>
   </si>
   <si>
+    <t>Ушакова Н.В./Габеркорн А.И.</t>
+  </si>
+  <si>
+    <t>Ходосова Д.А.</t>
+  </si>
+  <si>
     <t>Мировая политика и международные отношения (пр), Г209//</t>
   </si>
   <si>
@@ -266,6 +317,12 @@
     <t>Элективные дисциплины по физической культуре и спорту проводятся  4 парой или  5 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
+    <t>Калинина Е.А./Осипова А.В.</t>
+  </si>
+  <si>
     <t>//Современная российская политика (пр), Г209</t>
   </si>
   <si>
@@ -327,6 +384,12 @@
   </si>
   <si>
     <t>Учебная практика, ознакомительная практика, Г209</t>
+  </si>
+  <si>
+    <t>Афян К.А</t>
+  </si>
+  <si>
+    <t>Пичуева А.В.</t>
   </si>
   <si>
     <t>Иностранный язык, п/г 1, А502</t>
@@ -450,7 +513,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -469,6 +532,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -480,7 +549,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -597,6 +666,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -728,6 +810,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1073,7 +1168,7 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1081,10 +1176,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1182,7 +1297,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="272">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1222,24 +1337,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1252,6 +1370,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
@@ -1261,6 +1380,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1270,44 +1391,45 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1320,26 +1442,370 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1347,270 +1813,77 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1618,141 +1891,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2061,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2070,10 +2217,11 @@
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2081,15 +2229,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2097,13 +2245,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2113,22 +2261,22 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
@@ -2143,385 +2291,454 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="99" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="C9" s="120" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="G10" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="100"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="102"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="121"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="123"/>
+      <c r="G11" s="94"/>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="103" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="105"/>
-    </row>
-    <row r="13" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="96" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="97"/>
+      <c r="E12" s="97"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="93" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="105"/>
-    </row>
-    <row r="14" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C13" s="96" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="97"/>
+      <c r="E13" s="97"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="93" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
         <v>5</v>
       </c>
-      <c r="C14" s="106" t="s">
+      <c r="C14" s="124" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="126"/>
+      <c r="G14" s="92" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="25">
+        <v>1</v>
+      </c>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="75"/>
+    </row>
+    <row r="16" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="102" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="31"/>
+      <c r="B18" s="30">
+        <v>4</v>
+      </c>
+      <c r="C18" s="111" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="90" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="25">
+        <v>1</v>
+      </c>
+      <c r="C19" s="108" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="109"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="89" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>3</v>
+      </c>
+      <c r="C20" s="96"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="98"/>
+      <c r="G20" s="87" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>4</v>
+      </c>
+      <c r="C21" s="114" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="116"/>
+      <c r="G21" s="77" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="30">
+        <v>5</v>
+      </c>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="25">
+        <v>3</v>
+      </c>
+      <c r="C23" s="108"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="91"/>
+    </row>
+    <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>4</v>
+      </c>
+      <c r="C24" s="133" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="87" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>5</v>
+      </c>
+      <c r="C25" s="99" t="s">
+        <v>91</v>
+      </c>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="30">
+        <v>6</v>
+      </c>
+      <c r="C26" s="130"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="75"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="25">
+        <v>1</v>
+      </c>
+      <c r="C27" s="139" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="140"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="27">
+        <v>2</v>
+      </c>
+      <c r="C28" s="114" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="116"/>
+      <c r="G28" s="78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="106"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="107"/>
+      <c r="G29" s="88" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="30">
+        <v>5</v>
+      </c>
+      <c r="C30" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="143"/>
+      <c r="E30" s="143"/>
+      <c r="F30" s="144"/>
+      <c r="G30" s="90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="25">
+        <v>1</v>
+      </c>
+      <c r="C31" s="145" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="107"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="108"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="24">
-        <v>1</v>
-      </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="111"/>
-    </row>
-    <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="D31" s="146"/>
+      <c r="E31" s="146"/>
+      <c r="F31" s="147"/>
+      <c r="G31" s="33"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27">
         <v>2</v>
       </c>
-      <c r="C16" s="115" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="117"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C32" s="151"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="78"/>
+    </row>
+    <row r="33" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="38"/>
+      <c r="B33" s="30">
         <v>3</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C33" s="154"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="87"/>
+    </row>
+    <row r="34" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="39"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="42"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="43"/>
+      <c r="B35" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="145" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="146"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="147"/>
+      <c r="G35" s="89" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="63"/>
+      <c r="B36" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="114" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="63"/>
+      <c r="B37" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="148" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="149"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="150"/>
+      <c r="G37" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="83"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="28">
-        <v>4</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="123"/>
-    </row>
-    <row r="19" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="24">
-        <v>1</v>
-      </c>
-      <c r="C19" s="118" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>3</v>
-      </c>
-      <c r="C20" s="103"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="46"/>
+      <c r="B38" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="80" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="105"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>4</v>
-      </c>
-      <c r="C21" s="78" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="80"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28">
-        <v>5</v>
-      </c>
-      <c r="C22" s="124"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="126"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="24">
-        <v>3</v>
-      </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
-    </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>4</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="71"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>5</v>
-      </c>
-      <c r="C25" s="112" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="114"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28">
-        <v>6</v>
-      </c>
-      <c r="C26" s="66"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="68"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24">
-        <v>1</v>
-      </c>
-      <c r="C27" s="75" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="77"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="26">
-        <v>2</v>
-      </c>
-      <c r="C28" s="78" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="80"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="81" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="82"/>
-      <c r="E29" s="82"/>
-      <c r="F29" s="83"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="28">
-        <v>5</v>
-      </c>
-      <c r="C30" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="86"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="24">
-        <v>1</v>
-      </c>
-      <c r="C31" s="87" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="89"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>2</v>
-      </c>
-      <c r="C32" s="93"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="95"/>
-    </row>
-    <row r="33" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="34"/>
-      <c r="B33" s="28">
-        <v>3</v>
-      </c>
-      <c r="C33" s="96"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="98"/>
-    </row>
-    <row r="34" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="35"/>
-      <c r="B34" s="36"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="38"/>
-      <c r="B35" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="87" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="89"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="57"/>
-      <c r="B36" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="57"/>
-      <c r="B37" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="90" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="91"/>
-      <c r="E37" s="91"/>
-      <c r="F37" s="92"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="41"/>
-      <c r="B38" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="C38" s="72" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="74"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A40" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>16</v>
       </c>
@@ -2531,23 +2748,6 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C38:F38"/>
@@ -2561,6 +2761,23 @@
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -2583,7 +2800,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2592,10 +2809,11 @@
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2603,15 +2821,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2619,13 +2837,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2635,22 +2853,22 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
@@ -2665,383 +2883,443 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="120" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="25">
+        <v>1</v>
+      </c>
+      <c r="C11" s="167"/>
+      <c r="D11" s="168"/>
+      <c r="E11" s="168"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="33"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>2</v>
+      </c>
+      <c r="C12" s="170" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="171"/>
+      <c r="E12" s="171"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>3</v>
+      </c>
+      <c r="C13" s="173" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="174"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="87" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="176" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="177"/>
+      <c r="E14" s="177"/>
+      <c r="F14" s="178"/>
+      <c r="G14" s="32"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="25">
+        <v>1</v>
+      </c>
+      <c r="C15" s="179"/>
+      <c r="D15" s="180"/>
+      <c r="E15" s="180"/>
+      <c r="F15" s="181"/>
+      <c r="G15" s="74"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="101"/>
+      <c r="G16" s="78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="170" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="171"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="172"/>
+      <c r="G17" s="78" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="31"/>
+      <c r="B18" s="30">
+        <v>4</v>
+      </c>
+      <c r="C18" s="185"/>
+      <c r="D18" s="186"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="76"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="25">
+        <v>1</v>
+      </c>
+      <c r="C19" s="194" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="195"/>
+      <c r="E19" s="195" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="196"/>
+      <c r="G19" s="83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>2</v>
+      </c>
+      <c r="C20" s="191" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="192"/>
+      <c r="E20" s="192"/>
+      <c r="F20" s="193"/>
+      <c r="G20" s="87" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>3</v>
+      </c>
+      <c r="C21" s="161"/>
+      <c r="D21" s="162"/>
+      <c r="E21" s="162"/>
+      <c r="F21" s="163"/>
+      <c r="G21" s="87"/>
+    </row>
+    <row r="22" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="30">
+        <v>4</v>
+      </c>
+      <c r="C22" s="164"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="86"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="25">
+        <v>1</v>
+      </c>
+      <c r="C23" s="182"/>
+      <c r="D23" s="183"/>
+      <c r="E23" s="183"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="74"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>2</v>
+      </c>
+      <c r="C24" s="188" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="189"/>
+      <c r="E24" s="189"/>
+      <c r="F24" s="190"/>
+      <c r="G24" s="87" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="170" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="171"/>
+      <c r="E25" s="171"/>
+      <c r="F25" s="172"/>
+      <c r="G25" s="78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="200" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="201"/>
+      <c r="E26" s="201"/>
+      <c r="F26" s="202"/>
+      <c r="G26" s="76"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="25">
+        <v>1</v>
+      </c>
+      <c r="C27" s="158"/>
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="74"/>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="27">
+        <v>2</v>
+      </c>
+      <c r="C28" s="188" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="189"/>
+      <c r="E28" s="189"/>
+      <c r="F28" s="190"/>
+      <c r="G28" s="77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="173" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="175"/>
+      <c r="G29" s="77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="30">
+        <v>4</v>
+      </c>
+      <c r="C30" s="206"/>
+      <c r="D30" s="207"/>
+      <c r="E30" s="207"/>
+      <c r="F30" s="208"/>
+      <c r="G30" s="84"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="99" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="47"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="24">
-        <v>1</v>
-      </c>
-      <c r="C11" s="170"/>
-      <c r="D11" s="171"/>
-      <c r="E11" s="171"/>
-      <c r="F11" s="172"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="B31" s="25">
         <v>2</v>
       </c>
-      <c r="C12" s="151" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
-      <c r="F12" s="153"/>
-    </row>
-    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C31" s="194" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="195"/>
+      <c r="E31" s="195"/>
+      <c r="F31" s="196"/>
+      <c r="G31" s="83" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27">
         <v>3</v>
       </c>
-      <c r="C13" s="127" t="s">
+      <c r="C32" s="203" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="204"/>
+      <c r="E32" s="204"/>
+      <c r="F32" s="205"/>
+      <c r="G32" s="77" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="38"/>
+      <c r="B33" s="30">
+        <v>4</v>
+      </c>
+      <c r="C33" s="212"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="214"/>
+      <c r="G33" s="76"/>
+    </row>
+    <row r="34" spans="1:7" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="65"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="210"/>
+      <c r="E34" s="210"/>
+      <c r="F34" s="211"/>
+      <c r="G34" s="67"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="56"/>
+      <c r="B35" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="197" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="199"/>
+      <c r="G35" s="79" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="72"/>
+      <c r="B36" s="73" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="150"/>
+      <c r="G36" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="129"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="173" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="174"/>
-      <c r="E14" s="174"/>
-      <c r="F14" s="175"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="24">
-        <v>1</v>
-      </c>
-      <c r="C15" s="176"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="177"/>
-      <c r="F15" s="178"/>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>2</v>
-      </c>
-      <c r="C16" s="112" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="114"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>3</v>
-      </c>
-      <c r="C17" s="151" t="s">
-        <v>84</v>
-      </c>
-      <c r="D17" s="152"/>
-      <c r="E17" s="152"/>
-      <c r="F17" s="153"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="28">
-        <v>4</v>
-      </c>
-      <c r="C18" s="182"/>
-      <c r="D18" s="183"/>
-      <c r="E18" s="183"/>
-      <c r="F18" s="184"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="24">
-        <v>1</v>
-      </c>
-      <c r="C19" s="130" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="59"/>
+      <c r="B37" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="136" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="138"/>
+      <c r="G37" s="80" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="71"/>
+      <c r="C38" s="157" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="157"/>
+      <c r="E38" s="157"/>
+      <c r="F38" s="157"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="132"/>
-    </row>
-    <row r="20" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>2</v>
-      </c>
-      <c r="C20" s="148" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="150"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>3</v>
-      </c>
-      <c r="C21" s="164"/>
-      <c r="D21" s="165"/>
-      <c r="E21" s="165"/>
-      <c r="F21" s="166"/>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28">
-        <v>4</v>
-      </c>
-      <c r="C22" s="167"/>
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="169"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="24">
-        <v>1</v>
-      </c>
-      <c r="C23" s="179"/>
-      <c r="D23" s="180"/>
-      <c r="E23" s="180"/>
-      <c r="F23" s="181"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>2</v>
-      </c>
-      <c r="C24" s="133" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="134"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="135"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="151" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="153"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="157" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="158"/>
-      <c r="E26" s="158"/>
-      <c r="F26" s="159"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24">
-        <v>1</v>
-      </c>
-      <c r="C27" s="161"/>
-      <c r="D27" s="162"/>
-      <c r="E27" s="162"/>
-      <c r="F27" s="163"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="26">
-        <v>2</v>
-      </c>
-      <c r="C28" s="133" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="134"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="135"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="127" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="129"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="28">
-        <v>4</v>
-      </c>
-      <c r="C30" s="139"/>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
-      <c r="F30" s="141"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="24">
-        <v>2</v>
-      </c>
-      <c r="C31" s="130" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="132"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>3</v>
-      </c>
-      <c r="C32" s="136" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="138"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="34"/>
-      <c r="B33" s="28">
-        <v>4</v>
-      </c>
-      <c r="C33" s="145"/>
-      <c r="D33" s="146"/>
-      <c r="E33" s="146"/>
-      <c r="F33" s="147"/>
-    </row>
-    <row r="34" spans="1:6" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="59"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="142"/>
-      <c r="D34" s="143"/>
-      <c r="E34" s="143"/>
-      <c r="F34" s="144"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="51"/>
-      <c r="B35" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="154" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="156"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="64"/>
-      <c r="B36" s="65" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="90" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="92"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="54"/>
-      <c r="B37" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" s="72" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="74"/>
-    </row>
-    <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="63"/>
-      <c r="C38" s="160" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="160"/>
-      <c r="E38" s="160"/>
-      <c r="F38" s="160"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>16</v>
       </c>
@@ -3051,6 +3329,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C9:F9"/>
@@ -3067,20 +3359,6 @@
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C33:F33"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -3103,7 +3381,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3112,10 +3390,11 @@
     <col min="4" max="4" width="18.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3123,15 +3402,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3139,13 +3418,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -3155,22 +3434,22 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
@@ -3185,349 +3464,407 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="120" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="54">
+        <v>2</v>
+      </c>
+      <c r="C11" s="197" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="198"/>
+      <c r="E11" s="198"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="79" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="218" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="219"/>
+      <c r="E12" s="219"/>
+      <c r="F12" s="220"/>
+      <c r="G12" s="87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="221" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="222"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="223"/>
+      <c r="G13" s="78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30">
+        <v>5</v>
+      </c>
+      <c r="C14" s="99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="101"/>
+      <c r="G14" s="78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="25">
+        <v>2</v>
+      </c>
+      <c r="C15" s="260"/>
+      <c r="D15" s="269"/>
+      <c r="E15" s="270" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="271"/>
+      <c r="G15" s="95" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="170"/>
+      <c r="D16" s="171"/>
+      <c r="E16" s="171"/>
+      <c r="F16" s="172"/>
+      <c r="G16" s="81"/>
+    </row>
+    <row r="17" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="191" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="192"/>
+      <c r="E17" s="192"/>
+      <c r="F17" s="193"/>
+      <c r="G17" s="81" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="31"/>
+      <c r="B18" s="30">
+        <v>5</v>
+      </c>
+      <c r="C18" s="164"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="165"/>
+      <c r="F18" s="166"/>
+      <c r="G18" s="76"/>
+    </row>
+    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="25">
+        <v>1</v>
+      </c>
+      <c r="C19" s="215" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="216"/>
+      <c r="E19" s="216"/>
+      <c r="F19" s="217"/>
+      <c r="G19" s="87" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>2</v>
+      </c>
+      <c r="C20" s="99" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="101"/>
+      <c r="G20" s="78" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="68">
+        <v>3</v>
+      </c>
+      <c r="C21" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="100"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="78" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="30">
+        <v>4</v>
+      </c>
+      <c r="C22" s="136" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="25">
+        <v>1</v>
+      </c>
+      <c r="C23" s="215"/>
+      <c r="D23" s="216"/>
+      <c r="E23" s="216"/>
+      <c r="F23" s="217"/>
+      <c r="G23" s="77"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>2</v>
+      </c>
+      <c r="C24" s="218" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="219"/>
+      <c r="E24" s="219"/>
+      <c r="F24" s="220"/>
+      <c r="G24" s="87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
+      <c r="G25" s="78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="30">
+        <v>4</v>
+      </c>
+      <c r="C26" s="185"/>
+      <c r="D26" s="186"/>
+      <c r="E26" s="186"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="80"/>
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="233" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="234"/>
+      <c r="E27" s="234"/>
+      <c r="F27" s="235"/>
+      <c r="G27" s="75"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="27">
+        <v>4</v>
+      </c>
+      <c r="C28" s="218" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" s="219"/>
+      <c r="E28" s="219"/>
+      <c r="F28" s="220"/>
+      <c r="G28" s="77" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="27">
+        <v>5</v>
+      </c>
+      <c r="C29" s="227"/>
+      <c r="D29" s="228"/>
+      <c r="E29" s="228"/>
+      <c r="F29" s="229"/>
+      <c r="G29" s="77"/>
+    </row>
+    <row r="30" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="30">
+        <v>6</v>
+      </c>
+      <c r="C30" s="230"/>
+      <c r="D30" s="231"/>
+      <c r="E30" s="231"/>
+      <c r="F30" s="232"/>
+      <c r="G30" s="84"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="99" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="99"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="47"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="49">
+      <c r="B31" s="54">
+        <v>1</v>
+      </c>
+      <c r="C31" s="194" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="195"/>
+      <c r="E31" s="195"/>
+      <c r="F31" s="196"/>
+      <c r="G31" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="154" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="155"/>
-      <c r="E11" s="155"/>
-      <c r="F11" s="156"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C32" s="99" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="101"/>
+      <c r="G32" s="77" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="37"/>
+      <c r="B33" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="192" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="194"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
-        <v>4</v>
-      </c>
-      <c r="C13" s="207" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="208"/>
-      <c r="E13" s="208"/>
-      <c r="F13" s="209"/>
-    </row>
-    <row r="14" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
-        <v>5</v>
-      </c>
-      <c r="C14" s="112" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
-    </row>
-    <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="24">
-        <v>2</v>
-      </c>
-      <c r="C15" s="185"/>
-      <c r="D15" s="186"/>
-      <c r="E15" s="187" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="188"/>
-    </row>
-    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>3</v>
-      </c>
-      <c r="C16" s="151"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="153"/>
-    </row>
-    <row r="17" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>4</v>
-      </c>
-      <c r="C17" s="148" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="150"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="28">
-        <v>5</v>
-      </c>
-      <c r="C18" s="167"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="169"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="24">
-        <v>1</v>
-      </c>
-      <c r="C19" s="204" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="205"/>
-      <c r="E19" s="205"/>
-      <c r="F19" s="206"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>2</v>
-      </c>
-      <c r="C20" s="112" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="113"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="114"/>
-    </row>
-    <row r="21" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="61">
-        <v>3</v>
-      </c>
-      <c r="C21" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="114"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28">
-        <v>4</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="74"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="24">
-        <v>1</v>
-      </c>
-      <c r="C23" s="204"/>
-      <c r="D23" s="205"/>
-      <c r="E23" s="205"/>
-      <c r="F23" s="206"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>2</v>
-      </c>
-      <c r="C24" s="192" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="193"/>
-      <c r="E24" s="193"/>
-      <c r="F24" s="194"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="112" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" s="113"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="114"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28">
-        <v>4</v>
-      </c>
-      <c r="C26" s="182"/>
-      <c r="D26" s="183"/>
-      <c r="E26" s="183"/>
-      <c r="F26" s="184"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="201" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="202"/>
-      <c r="E27" s="202"/>
-      <c r="F27" s="203"/>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="26">
-        <v>4</v>
-      </c>
-      <c r="C28" s="192" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="193"/>
-      <c r="E28" s="193"/>
-      <c r="F28" s="194"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="26">
-        <v>5</v>
-      </c>
-      <c r="C29" s="195"/>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="197"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="28">
-        <v>6</v>
-      </c>
-      <c r="C30" s="198"/>
-      <c r="D30" s="199"/>
-      <c r="E30" s="199"/>
-      <c r="F30" s="200"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="49">
-        <v>1</v>
-      </c>
-      <c r="C31" s="130" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="132"/>
-    </row>
-    <row r="32" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>2</v>
-      </c>
-      <c r="C32" s="112" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="114"/>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="33"/>
-      <c r="B33" s="26">
-        <v>3</v>
-      </c>
-      <c r="C33" s="93"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="95"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="52"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="189"/>
-      <c r="D34" s="190"/>
-      <c r="E34" s="190"/>
-      <c r="F34" s="191"/>
-    </row>
-    <row r="35" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="62" t="s">
-        <v>49</v>
-      </c>
-      <c r="B35" s="63"/>
-      <c r="C35" s="160" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35" s="160"/>
-      <c r="E35" s="160"/>
-      <c r="F35" s="160"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="151"/>
+      <c r="D33" s="152"/>
+      <c r="E33" s="152"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="75"/>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="57"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="226"/>
+      <c r="G34" s="32"/>
+    </row>
+    <row r="35" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="71"/>
+      <c r="C35" s="157" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="157"/>
+      <c r="E35" s="157"/>
+      <c r="F35" s="157"/>
+      <c r="G35" s="69"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>16</v>
       </c>
@@ -3537,6 +3874,20 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C25:F25"/>
@@ -3551,20 +3902,6 @@
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -3587,7 +3924,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3595,10 +3932,11 @@
     <col min="3" max="3" width="22.28515625" style="2" customWidth="1"/>
     <col min="4" max="5" width="21" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3606,15 +3944,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3622,13 +3960,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -3638,22 +3976,22 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
@@ -3668,319 +4006,366 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="12"/>
       <c r="C10" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-    </row>
-    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="49">
+      <c r="C11" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="50"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="54">
         <v>2</v>
       </c>
-      <c r="C12" s="201" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="203"/>
-    </row>
-    <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="233" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="234"/>
+      <c r="E12" s="234"/>
+      <c r="F12" s="235"/>
+      <c r="G12" s="87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <v>3</v>
       </c>
-      <c r="C13" s="148"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="150"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="191"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="193"/>
+      <c r="G13" s="87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>4</v>
       </c>
-      <c r="C14" s="215"/>
-      <c r="D14" s="216"/>
-      <c r="E14" s="216"/>
-      <c r="F14" s="217"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="266"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="267"/>
+      <c r="F14" s="268"/>
+      <c r="G14" s="78"/>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="29"/>
+      <c r="B15" s="30">
         <v>5</v>
       </c>
-      <c r="C15" s="182"/>
-      <c r="D15" s="183"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="184"/>
-    </row>
-    <row r="16" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="24">
+      <c r="C15" s="185"/>
+      <c r="D15" s="186"/>
+      <c r="E15" s="186"/>
+      <c r="F15" s="187"/>
+      <c r="G15" s="80"/>
+    </row>
+    <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="185"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
-      <c r="F16" s="211"/>
-    </row>
-    <row r="17" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="260"/>
+      <c r="D16" s="261"/>
+      <c r="E16" s="261"/>
+      <c r="F16" s="262"/>
+      <c r="G16" s="81"/>
+    </row>
+    <row r="17" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <v>3</v>
       </c>
-      <c r="C17" s="212"/>
-      <c r="D17" s="213"/>
-      <c r="E17" s="213"/>
-      <c r="F17" s="214"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="C17" s="263"/>
+      <c r="D17" s="264"/>
+      <c r="E17" s="264"/>
+      <c r="F17" s="265"/>
+      <c r="G17" s="81"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <v>4</v>
       </c>
-      <c r="C18" s="218" t="s">
+      <c r="C18" s="242" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="T18" s="61"/>
+    </row>
+    <row r="19" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="31"/>
+      <c r="B19" s="30">
+        <v>5</v>
+      </c>
+      <c r="C19" s="136" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="80" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="25">
+        <v>3</v>
+      </c>
+      <c r="C20" s="170" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="171"/>
+      <c r="E20" s="171"/>
+      <c r="F20" s="172"/>
+      <c r="G20" s="78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>4</v>
+      </c>
+      <c r="C21" s="170" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" s="171"/>
+      <c r="E21" s="171"/>
+      <c r="F21" s="172"/>
+      <c r="G21" s="78" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="31"/>
+      <c r="B22" s="30">
+        <v>5</v>
+      </c>
+      <c r="C22" s="251" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="252"/>
+      <c r="E22" s="252"/>
+      <c r="F22" s="253"/>
+      <c r="G22" s="80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="25">
+        <v>2</v>
+      </c>
+      <c r="C23" s="254"/>
+      <c r="D23" s="255"/>
+      <c r="E23" s="255"/>
+      <c r="F23" s="256"/>
+      <c r="G23" s="79"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>3</v>
+      </c>
+      <c r="C24" s="257"/>
+      <c r="D24" s="258"/>
+      <c r="E24" s="258"/>
+      <c r="F24" s="259"/>
+      <c r="G24" s="78"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>4</v>
+      </c>
+      <c r="C25" s="221" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="222"/>
+      <c r="E25" s="222"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="31"/>
+      <c r="B26" s="30">
+        <v>5</v>
+      </c>
+      <c r="C26" s="148" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="150"/>
+      <c r="G26" s="78" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="25">
+        <v>2</v>
+      </c>
+      <c r="C27" s="239"/>
+      <c r="D27" s="240"/>
+      <c r="E27" s="240"/>
+      <c r="F27" s="241"/>
+      <c r="G27" s="33"/>
+    </row>
+    <row r="28" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="34"/>
+      <c r="B28" s="68">
+        <v>3</v>
+      </c>
+      <c r="C28" s="148" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="149"/>
+      <c r="E28" s="149"/>
+      <c r="F28" s="150"/>
+      <c r="G28" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="219"/>
-      <c r="E18" s="219"/>
-      <c r="F18" s="220"/>
-      <c r="S18" s="56"/>
-    </row>
-    <row r="19" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="29"/>
-      <c r="B19" s="28">
+    </row>
+    <row r="29" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="34"/>
+      <c r="B29" s="68">
+        <v>4</v>
+      </c>
+      <c r="C29" s="242" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="243"/>
+      <c r="E29" s="243"/>
+      <c r="F29" s="244"/>
+      <c r="G29" s="78" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="35"/>
+      <c r="B30" s="30">
         <v>5</v>
       </c>
-      <c r="C19" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="74"/>
-    </row>
-    <row r="20" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="24">
+      <c r="C30" s="245"/>
+      <c r="D30" s="246"/>
+      <c r="E30" s="246"/>
+      <c r="F30" s="247"/>
+      <c r="G30" s="32"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A31" s="55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="54">
+        <v>1</v>
+      </c>
+      <c r="C31" s="248" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="249"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="250"/>
+      <c r="G31" s="62"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.4">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27">
+        <v>2</v>
+      </c>
+      <c r="C32" s="236"/>
+      <c r="D32" s="237"/>
+      <c r="E32" s="237"/>
+      <c r="F32" s="238"/>
+      <c r="G32" s="28"/>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="57"/>
+      <c r="B33" s="58">
         <v>3</v>
       </c>
-      <c r="C20" s="151" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="153"/>
-    </row>
-    <row r="21" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>4</v>
-      </c>
-      <c r="C21" s="151" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="153"/>
-    </row>
-    <row r="22" spans="1:19" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28">
-        <v>5</v>
-      </c>
-      <c r="C22" s="221" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="223"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A23" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="24">
-        <v>2</v>
-      </c>
-      <c r="C23" s="224"/>
-      <c r="D23" s="225"/>
-      <c r="E23" s="225"/>
-      <c r="F23" s="226"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>3</v>
-      </c>
-      <c r="C24" s="227"/>
-      <c r="D24" s="228"/>
-      <c r="E24" s="228"/>
-      <c r="F24" s="229"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>4</v>
-      </c>
-      <c r="C25" s="207" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" s="208"/>
-      <c r="E25" s="208"/>
-      <c r="F25" s="209"/>
-    </row>
-    <row r="26" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28">
-        <v>5</v>
-      </c>
-      <c r="C26" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="92"/>
-    </row>
-    <row r="27" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24">
-        <v>2</v>
-      </c>
-      <c r="C27" s="233"/>
-      <c r="D27" s="234"/>
-      <c r="E27" s="234"/>
-      <c r="F27" s="235"/>
-    </row>
-    <row r="28" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="61">
-        <v>3</v>
-      </c>
-      <c r="C28" s="90" t="s">
-        <v>61</v>
-      </c>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="92"/>
-    </row>
-    <row r="29" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="61">
-        <v>4</v>
-      </c>
-      <c r="C29" s="218" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29" s="219"/>
-      <c r="E29" s="219"/>
-      <c r="F29" s="220"/>
-    </row>
-    <row r="30" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="28">
-        <v>5</v>
-      </c>
-      <c r="C30" s="236"/>
-      <c r="D30" s="237"/>
-      <c r="E30" s="237"/>
-      <c r="F30" s="238"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A31" s="50" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="49">
-        <v>1</v>
-      </c>
-      <c r="C31" s="239" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="241"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>2</v>
-      </c>
-      <c r="C32" s="230"/>
-      <c r="D32" s="231"/>
-      <c r="E32" s="231"/>
-      <c r="F32" s="232"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="52"/>
-      <c r="B33" s="53">
-        <v>3</v>
-      </c>
-      <c r="C33" s="145"/>
-      <c r="D33" s="146"/>
-      <c r="E33" s="146"/>
-      <c r="F33" s="147"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="212"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
+      <c r="F33" s="214"/>
+      <c r="G33" s="32"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>16</v>
       </c>
@@ -3990,6 +4375,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C26:F26"/>
@@ -3998,22 +4399,6 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
   </mergeCells>
   <conditionalFormatting sqref="C10">
     <cfRule type="expression" priority="3">
